--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64627E67-AB5F-4580-BD19-7103368506A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{393BB085-8562-4C56-9F85-8DA9F0F9FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{393BB085-8562-4C56-9F85-8DA9F0F9FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E638935E-1AE2-4EF8-9B70-F14CF65FC1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E638935E-1AE2-4EF8-9B70-F14CF65FC1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50092315-6E5F-458E-8C97-1D205392703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -263,6 +263,33 @@
   </si>
   <si>
     <t>ELC_wo*</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>flo_emis</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>co2captured</t>
+  </si>
+  <si>
+    <t>*ccs*</t>
+  </si>
+  <si>
+    <t>coal,oil,bioenergy</t>
   </si>
   <si>
     <t>~replicateinregions</t>
@@ -904,16 +931,16 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -921,10 +948,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -933,10 +960,10 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
         <v>21</v>
@@ -945,10 +972,10 @@
         <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -957,10 +984,10 @@
         <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="T10" t="s">
         <v>21</v>
@@ -968,1052 +995,1052 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J11" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R11" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="S11" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="T11" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="J12" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M12" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="T12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J13" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="O13" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R13" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="S13" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="T13" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O14" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="T14" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I15" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O15" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R15" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="S15" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="T15" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" t="s">
         <v>143</v>
       </c>
-      <c r="I16" t="s">
-        <v>144</v>
-      </c>
-      <c r="J16" t="s">
-        <v>134</v>
-      </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M16" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="N16" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="O16" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="S16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N17" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O17" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R17" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S17" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="T17" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N18" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O18" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R18" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="S18" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="T18" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="S19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="T19" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O20" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R20" t="s">
+        <v>178</v>
+      </c>
+      <c r="S20" t="s">
+        <v>179</v>
+      </c>
+      <c r="T20" t="s">
         <v>169</v>
-      </c>
-      <c r="S20" t="s">
-        <v>170</v>
-      </c>
-      <c r="T20" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="N21" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="O21" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" t="s">
         <v>103</v>
       </c>
-      <c r="E22" t="s">
-        <v>81</v>
-      </c>
-      <c r="L22" t="s">
-        <v>78</v>
-      </c>
-      <c r="M22" t="s">
-        <v>94</v>
-      </c>
       <c r="N22" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O22" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" t="s">
+        <v>87</v>
+      </c>
+      <c r="M23" t="s">
         <v>105</v>
       </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" t="s">
-        <v>96</v>
-      </c>
       <c r="N23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="O23" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s">
+        <v>87</v>
+      </c>
+      <c r="M24" t="s">
         <v>107</v>
       </c>
-      <c r="E24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" t="s">
-        <v>78</v>
-      </c>
-      <c r="M24" t="s">
-        <v>98</v>
-      </c>
       <c r="N24" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="O24" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" t="s">
+        <v>90</v>
+      </c>
+      <c r="L25" t="s">
+        <v>87</v>
+      </c>
+      <c r="M25" t="s">
         <v>109</v>
       </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="L25" t="s">
-        <v>78</v>
-      </c>
-      <c r="M25" t="s">
-        <v>100</v>
-      </c>
       <c r="N25" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="O25" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" t="s">
+        <v>87</v>
+      </c>
+      <c r="M26" t="s">
         <v>111</v>
       </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="L26" t="s">
-        <v>78</v>
-      </c>
-      <c r="M26" t="s">
-        <v>102</v>
-      </c>
       <c r="N26" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="O26" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" t="s">
+        <v>87</v>
+      </c>
+      <c r="M27" t="s">
         <v>113</v>
       </c>
-      <c r="E27" t="s">
-        <v>81</v>
-      </c>
-      <c r="L27" t="s">
-        <v>78</v>
-      </c>
-      <c r="M27" t="s">
-        <v>104</v>
-      </c>
       <c r="N27" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="O27" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" t="s">
+        <v>90</v>
+      </c>
+      <c r="L28" t="s">
+        <v>87</v>
+      </c>
+      <c r="M28" t="s">
         <v>115</v>
       </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="L28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M28" t="s">
-        <v>106</v>
-      </c>
       <c r="N28" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="O28" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" t="s">
+        <v>90</v>
+      </c>
+      <c r="L29" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" t="s">
         <v>117</v>
       </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="L29" t="s">
-        <v>78</v>
-      </c>
-      <c r="M29" t="s">
-        <v>108</v>
-      </c>
       <c r="N29" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="O29" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>90</v>
+      </c>
+      <c r="L30" t="s">
+        <v>87</v>
+      </c>
+      <c r="M30" t="s">
         <v>119</v>
       </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="L30" t="s">
-        <v>78</v>
-      </c>
-      <c r="M30" t="s">
-        <v>110</v>
-      </c>
       <c r="N30" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="O30" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" t="s">
+        <v>90</v>
+      </c>
+      <c r="L31" t="s">
+        <v>87</v>
+      </c>
+      <c r="M31" t="s">
         <v>121</v>
       </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31" t="s">
-        <v>112</v>
-      </c>
       <c r="N31" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O31" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" t="s">
+        <v>90</v>
+      </c>
+      <c r="L32" t="s">
+        <v>87</v>
+      </c>
+      <c r="M32" t="s">
         <v>123</v>
       </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" t="s">
-        <v>78</v>
-      </c>
-      <c r="M32" t="s">
-        <v>114</v>
-      </c>
       <c r="N32" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="O32" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" t="s">
+        <v>90</v>
+      </c>
+      <c r="L33" t="s">
+        <v>87</v>
+      </c>
+      <c r="M33" t="s">
         <v>125</v>
       </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
-      <c r="L33" t="s">
-        <v>78</v>
-      </c>
-      <c r="M33" t="s">
-        <v>116</v>
-      </c>
       <c r="N33" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O33" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="L34" t="s">
+        <v>87</v>
+      </c>
+      <c r="M34" t="s">
         <v>127</v>
       </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="L34" t="s">
-        <v>78</v>
-      </c>
-      <c r="M34" t="s">
-        <v>118</v>
-      </c>
       <c r="N34" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="O34" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" t="s">
+        <v>90</v>
+      </c>
+      <c r="L35" t="s">
+        <v>87</v>
+      </c>
+      <c r="M35" t="s">
         <v>129</v>
       </c>
-      <c r="E35" t="s">
-        <v>81</v>
-      </c>
-      <c r="L35" t="s">
-        <v>78</v>
-      </c>
-      <c r="M35" t="s">
-        <v>120</v>
-      </c>
       <c r="N35" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="O35" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" t="s">
+        <v>90</v>
+      </c>
+      <c r="L36" t="s">
+        <v>87</v>
+      </c>
+      <c r="M36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" t="s">
-        <v>81</v>
-      </c>
-      <c r="L36" t="s">
-        <v>78</v>
-      </c>
-      <c r="M36" t="s">
-        <v>122</v>
-      </c>
       <c r="N36" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="O36" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L37" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M37" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N37" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="O37" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L38" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M38" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N38" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="O38" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L39" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M39" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="O39" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L40" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M40" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="N40" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O40" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L41" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M41" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N41" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="O41" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L42" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M42" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="N42" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="O42" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L43" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M43" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="N43" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="O43" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L44" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M44" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="N44" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="O44" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L45" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="N45" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="O45" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L46" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M46" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="N46" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="O46" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L47" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M47" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N47" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="O47" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L48" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M48" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N48" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L49" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M49" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="N49" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="O49" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X50"/>
+  <dimension ref="C4:X57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -3410,7 +3437,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -3424,7 +3451,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -3436,6 +3463,86 @@
       </c>
       <c r="F50" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" t="s">
+        <v>65</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" t="s">
+        <v>66</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2022</v>
+      </c>
+      <c r="J55">
+        <v>2030</v>
+      </c>
+      <c r="K55" t="s">
+        <v>76</v>
+      </c>
+      <c r="L55" t="s">
+        <v>77</v>
+      </c>
+      <c r="M55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" t="s">
+        <v>82</v>
+      </c>
+      <c r="I56">
+        <v>0.95</v>
+      </c>
+      <c r="L56" t="s">
+        <v>80</v>
+      </c>
+      <c r="M56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="I57">
+        <v>0.85</v>
+      </c>
+      <c r="L57" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50092315-6E5F-458E-8C97-1D205392703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5DE122C-61A2-4B60-8B51-00ACD4E0F4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="180">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -304,280 +304,280 @@
     <t>ZAF</t>
   </si>
   <si>
-    <t>w836844162-400</t>
-  </si>
-  <si>
-    <t>at grid node - w836844162-400</t>
+    <t>w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w836844162-400_ZAF</t>
   </si>
   <si>
     <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
   </si>
   <si>
-    <t>w107391770-400</t>
-  </si>
-  <si>
-    <t>at grid node - w107391770-400</t>
-  </si>
-  <si>
-    <t>w169647963-400</t>
-  </si>
-  <si>
-    <t>at grid node - w169647963-400</t>
-  </si>
-  <si>
-    <t>w120941269-400</t>
-  </si>
-  <si>
-    <t>at grid node - w120941269-400</t>
-  </si>
-  <si>
-    <t>w107431792-400</t>
-  </si>
-  <si>
-    <t>at grid node - w107431792-400</t>
-  </si>
-  <si>
-    <t>w83525879-400</t>
-  </si>
-  <si>
-    <t>at grid node - w83525879-400</t>
-  </si>
-  <si>
-    <t>w131625968-400</t>
-  </si>
-  <si>
-    <t>at grid node - w131625968-400</t>
-  </si>
-  <si>
-    <t>w179140081-400</t>
-  </si>
-  <si>
-    <t>at grid node - w179140081-400</t>
-  </si>
-  <si>
-    <t>w220129604-400</t>
-  </si>
-  <si>
-    <t>at grid node - w220129604-400</t>
-  </si>
-  <si>
-    <t>w238322344-400</t>
-  </si>
-  <si>
-    <t>at grid node - w238322344-400</t>
-  </si>
-  <si>
-    <t>w185171518-400</t>
-  </si>
-  <si>
-    <t>at grid node - w185171518-400</t>
-  </si>
-  <si>
-    <t>w98231311-400</t>
-  </si>
-  <si>
-    <t>at grid node - w98231311-400</t>
-  </si>
-  <si>
-    <t>w209976655-400</t>
-  </si>
-  <si>
-    <t>at grid node - w209976655-400</t>
-  </si>
-  <si>
-    <t>w185497473-400</t>
-  </si>
-  <si>
-    <t>at grid node - w185497473-400</t>
-  </si>
-  <si>
-    <t>ZA22-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA22-400</t>
-  </si>
-  <si>
-    <t>ZA18-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA18-400</t>
-  </si>
-  <si>
-    <t>w105811523-400</t>
-  </si>
-  <si>
-    <t>at grid node - w105811523-400</t>
-  </si>
-  <si>
-    <t>w213181313-400</t>
-  </si>
-  <si>
-    <t>at grid node - w213181313-400</t>
-  </si>
-  <si>
-    <t>w182408147-400</t>
-  </si>
-  <si>
-    <t>at grid node - w182408147-400</t>
-  </si>
-  <si>
-    <t>w65600948-400</t>
-  </si>
-  <si>
-    <t>at grid node - w65600948-400</t>
-  </si>
-  <si>
-    <t>w200232961-400</t>
-  </si>
-  <si>
-    <t>at grid node - w200232961-400</t>
-  </si>
-  <si>
-    <t>ZA2-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA2-400</t>
-  </si>
-  <si>
-    <t>w455498147-400</t>
-  </si>
-  <si>
-    <t>at grid node - w455498147-400</t>
-  </si>
-  <si>
-    <t>ZA14-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA14-400</t>
-  </si>
-  <si>
-    <t>ZA15-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA15-400</t>
-  </si>
-  <si>
-    <t>w209365700-400</t>
-  </si>
-  <si>
-    <t>at grid node - w209365700-400</t>
-  </si>
-  <si>
-    <t>w105759402-400</t>
-  </si>
-  <si>
-    <t>at grid node - w105759402-400</t>
+    <t>w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>w120941269-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w120941269-400_ZAF</t>
+  </si>
+  <si>
+    <t>w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>w179140081-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w179140081-400_ZAF</t>
+  </si>
+  <si>
+    <t>w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>w209976655-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w209976655-400_ZAF</t>
+  </si>
+  <si>
+    <t>w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA22-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA22-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>w65600948-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w65600948-400_ZAF</t>
+  </si>
+  <si>
+    <t>w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>w455498147-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w455498147-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA14-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA14-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA15-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA15-400_ZAF</t>
+  </si>
+  <si>
+    <t>w209365700-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w209365700-400_ZAF</t>
+  </si>
+  <si>
+    <t>w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w105759402-400_ZAF</t>
   </si>
   <si>
     <t>EN_Hydro_ZAF-1,EN_Hydro_ZAF-2,EN_Hydro_ZAF-3</t>
   </si>
   <si>
-    <t>w142414070-765</t>
-  </si>
-  <si>
-    <t>at grid node - w142414070-765</t>
-  </si>
-  <si>
-    <t>ZA26-400</t>
-  </si>
-  <si>
-    <t>at grid node - ZA26-400</t>
-  </si>
-  <si>
-    <t>w102682082-400</t>
-  </si>
-  <si>
-    <t>at grid node - w102682082-400</t>
-  </si>
-  <si>
-    <t>w156418705-400</t>
-  </si>
-  <si>
-    <t>at grid node - w156418705-400</t>
-  </si>
-  <si>
-    <t>w631673098-400</t>
-  </si>
-  <si>
-    <t>at grid node - w631673098-400</t>
+    <t>w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>ZA26-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA26-400_ZAF</t>
+  </si>
+  <si>
+    <t>w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w631673098-400_ZAF</t>
   </si>
   <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>w62193952-400</t>
-  </si>
-  <si>
-    <t>at grid node - w62193952-400</t>
-  </si>
-  <si>
-    <t>w182042518-400</t>
-  </si>
-  <si>
-    <t>at grid node - w182042518-400</t>
-  </si>
-  <si>
-    <t>w169789536-400</t>
-  </si>
-  <si>
-    <t>at grid node - w169789536-400</t>
-  </si>
-  <si>
-    <t>r17287657-400</t>
-  </si>
-  <si>
-    <t>at grid node - r17287657-400</t>
-  </si>
-  <si>
-    <t>w142414070-400</t>
-  </si>
-  <si>
-    <t>at grid node - w142414070-400</t>
-  </si>
-  <si>
-    <t>w260486370-400</t>
-  </si>
-  <si>
-    <t>at grid node - w260486370-400</t>
-  </si>
-  <si>
-    <t>w102925909-400</t>
-  </si>
-  <si>
-    <t>at grid node - w102925909-400</t>
+    <t>w62193952-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w62193952-400_ZAF</t>
+  </si>
+  <si>
+    <t>w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>w102925909-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w102925909-400_ZAF</t>
+  </si>
+  <si>
+    <t>w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w359805008-400_ZAF</t>
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w92348290-765</t>
-  </si>
-  <si>
-    <t>at grid node - w92348290-765</t>
-  </si>
-  <si>
-    <t>w176362710-400</t>
-  </si>
-  <si>
-    <t>at grid node - w176362710-400</t>
-  </si>
-  <si>
-    <t>w178240552-400</t>
-  </si>
-  <si>
-    <t>at grid node - w178240552-400</t>
-  </si>
-  <si>
-    <t>w359805008-400</t>
-  </si>
-  <si>
-    <t>at grid node - w359805008-400</t>
-  </si>
-  <si>
-    <t>ZA28-765</t>
-  </si>
-  <si>
-    <t>at grid node - ZA28-765</t>
+    <t>w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>w104080393-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w104080393-400_ZAF</t>
+  </si>
+  <si>
+    <t>ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>at grid node - w200757306-400_ZAF</t>
   </si>
 </sst>
 </file>
@@ -1034,13 +1034,13 @@
         <v>87</v>
       </c>
       <c r="R11" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="S11" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="T11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -1084,13 +1084,13 @@
         <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="S12" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="T12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -1134,13 +1134,13 @@
         <v>87</v>
       </c>
       <c r="R13" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="S13" t="s">
+        <v>92</v>
+      </c>
+      <c r="T13" t="s">
         <v>171</v>
-      </c>
-      <c r="T13" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -1184,13 +1184,13 @@
         <v>87</v>
       </c>
       <c r="R14" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="S14" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="T14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1234,13 +1234,13 @@
         <v>87</v>
       </c>
       <c r="R15" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="S15" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="T15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1284,13 +1284,13 @@
         <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="T16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -1322,13 +1322,13 @@
         <v>87</v>
       </c>
       <c r="R17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="T17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -1360,13 +1360,13 @@
         <v>87</v>
       </c>
       <c r="R18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="T18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -1398,13 +1398,13 @@
         <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="S19" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="T19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -1431,18 +1431,6 @@
       </c>
       <c r="O20" t="s">
         <v>154</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>87</v>
-      </c>
-      <c r="R20" t="s">
-        <v>178</v>
-      </c>
-      <c r="S20" t="s">
-        <v>179</v>
-      </c>
-      <c r="T20" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5DE122C-61A2-4B60-8B51-00ACD4E0F4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BAE5531-F07A-4F1B-88D0-83215171FC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BAE5531-F07A-4F1B-88D0-83215171FC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0379BF39-863E-4FDE-ACF0-FFF026CC1674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0379BF39-863E-4FDE-ACF0-FFF026CC1674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F856920-DE8F-4925-B893-523D22653401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F856920-DE8F-4925-B893-523D22653401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DEA01EF-5B44-499F-B4A3-8ED655998583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DEA01EF-5B44-499F-B4A3-8ED655998583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C3BD8C7-0409-40CF-B64B-BD26CC69BD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C3BD8C7-0409-40CF-B64B-BD26CC69BD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E543DF-2442-426F-A25F-0E6F8533AB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="181">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>at grid node - w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elcagg*</t>
   </si>
 </sst>
 </file>
@@ -929,6 +932,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>84</v>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E543DF-2442-426F-A25F-0E6F8533AB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A62F4-B7AC-4309-AEBC-B068FBEE2CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A62F4-B7AC-4309-AEBC-B068FBEE2CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359BF10A-74FD-4CC7-A95C-64D4AA39AD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="188">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -310,9 +310,6 @@
     <t>at grid node - w836844162-400_ZAF</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
     <t>w107391770-400_ZAF</t>
   </si>
   <si>
@@ -581,13 +578,97 @@
   </si>
   <si>
     <t>elcagg*</t>
+  </si>
+  <si>
+    <r>
+      <t>w169647963-400_ZAF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Coega/PE, 24 km from port (LNG candidate, most advanced)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>w120941269-400_ZAF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Richards Bay, 15 km (LNG candidate)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>w107431792-400_ZAF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Saldanha, 32 km (LNG candidate)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>w836844162-400_ZAF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Cape Town / Atlantis, 27 km (Ankerlig retrofit + greenfield)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>w179140081-400_ZAF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Sasol Secunda, 7 km (existing pipeline-gas terminus, special</t>
+    </r>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+  </si>
+  <si>
+    <t>CCGT,CCGT + CCS</t>
+  </si>
+  <si>
+    <t>gas offered only on coastal buses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,6 +679,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -623,11 +718,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,15 +1005,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B3:T53"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:20">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:20">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -924,7 +1021,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:20">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -932,15 +1029,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:20">
       <c r="B6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:20">
       <c r="B9" t="s">
         <v>84</v>
       </c>
@@ -954,7 +1051,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:20">
       <c r="B10" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:20">
       <c r="B11" t="s">
         <v>87</v>
       </c>
@@ -1015,19 +1112,19 @@
         <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="G11" t="s">
         <v>87</v>
       </c>
       <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" t="s">
         <v>141</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>142</v>
-      </c>
-      <c r="J11" t="s">
-        <v>143</v>
       </c>
       <c r="L11" t="s">
         <v>87</v>
@@ -1039,1007 +1136,1118 @@
         <v>89</v>
       </c>
       <c r="O11" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R11" t="s">
+        <v>168</v>
+      </c>
+      <c r="S11" t="s">
+        <v>169</v>
+      </c>
+      <c r="T11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20">
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" t="s">
         <v>154</v>
       </c>
-      <c r="Q11" t="s">
-        <v>87</v>
-      </c>
-      <c r="R11" t="s">
-        <v>169</v>
-      </c>
-      <c r="S11" t="s">
+      <c r="N12" t="s">
+        <v>155</v>
+      </c>
+      <c r="O12" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R12" t="s">
+        <v>154</v>
+      </c>
+      <c r="S12" t="s">
+        <v>155</v>
+      </c>
+      <c r="T12" t="s">
         <v>170</v>
       </c>
-      <c r="T11" t="s">
+    </row>
+    <row r="13" spans="2:20">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J13" t="s">
+        <v>142</v>
+      </c>
+      <c r="L13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s">
+        <v>157</v>
+      </c>
+      <c r="O13" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13" t="s">
+        <v>90</v>
+      </c>
+      <c r="S13" t="s">
+        <v>91</v>
+      </c>
+      <c r="T13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" t="s">
+        <v>90</v>
+      </c>
+      <c r="N14" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" t="s">
+        <v>92</v>
+      </c>
+      <c r="S14" t="s">
+        <v>93</v>
+      </c>
+      <c r="T14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20">
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" t="s">
+        <v>92</v>
+      </c>
+      <c r="N15" t="s">
+        <v>93</v>
+      </c>
+      <c r="O15" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>87</v>
+      </c>
+      <c r="R15" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="S15" t="s">
+        <v>172</v>
+      </c>
+      <c r="T15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20">
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" t="s">
+        <v>152</v>
+      </c>
+      <c r="J16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M16" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" t="s">
+        <v>159</v>
+      </c>
+      <c r="O16" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>87</v>
+      </c>
+      <c r="R16" t="s">
+        <v>173</v>
+      </c>
+      <c r="S16" t="s">
+        <v>174</v>
+      </c>
+      <c r="T16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" t="s">
+        <v>94</v>
+      </c>
+      <c r="N17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O17" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>87</v>
+      </c>
+      <c r="R17" t="s">
+        <v>175</v>
+      </c>
+      <c r="S17" t="s">
+        <v>176</v>
+      </c>
+      <c r="T17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20">
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" t="s">
+        <v>185</v>
+      </c>
+      <c r="L18" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+      <c r="O18" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" t="s">
+        <v>177</v>
+      </c>
+      <c r="S18" t="s">
+        <v>178</v>
+      </c>
+      <c r="T18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" t="s">
+        <v>98</v>
+      </c>
+      <c r="N19" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>87</v>
+      </c>
+      <c r="R19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S19" t="s">
+        <v>159</v>
+      </c>
+      <c r="T19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" t="s">
+        <v>101</v>
+      </c>
+      <c r="O20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20">
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>185</v>
+      </c>
+      <c r="L21" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21" t="s">
+        <v>160</v>
+      </c>
+      <c r="N21" t="s">
+        <v>161</v>
+      </c>
+      <c r="O21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20">
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L22" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" t="s">
+        <v>102</v>
+      </c>
+      <c r="N22" t="s">
+        <v>103</v>
+      </c>
+      <c r="O22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20">
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>185</v>
+      </c>
+      <c r="L23" t="s">
+        <v>87</v>
+      </c>
+      <c r="M23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" t="s">
+        <v>105</v>
+      </c>
+      <c r="O23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20">
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>185</v>
+      </c>
+      <c r="L24" t="s">
+        <v>87</v>
+      </c>
+      <c r="M24" t="s">
+        <v>106</v>
+      </c>
+      <c r="N24" t="s">
+        <v>107</v>
+      </c>
+      <c r="O24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20">
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>185</v>
+      </c>
+      <c r="L25" t="s">
+        <v>87</v>
+      </c>
+      <c r="M25" t="s">
+        <v>108</v>
+      </c>
+      <c r="N25" t="s">
+        <v>109</v>
+      </c>
+      <c r="O25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20">
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>185</v>
+      </c>
+      <c r="L26" t="s">
+        <v>87</v>
+      </c>
+      <c r="M26" t="s">
+        <v>110</v>
+      </c>
+      <c r="N26" t="s">
+        <v>111</v>
+      </c>
+      <c r="O26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20">
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" t="s">
+        <v>87</v>
+      </c>
+      <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N27" t="s">
+        <v>113</v>
+      </c>
+      <c r="O27" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20">
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>185</v>
+      </c>
+      <c r="L28" t="s">
+        <v>87</v>
+      </c>
+      <c r="M28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N28" t="s">
+        <v>115</v>
+      </c>
+      <c r="O28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20">
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>185</v>
+      </c>
+      <c r="L29" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" t="s">
+        <v>116</v>
+      </c>
+      <c r="N29" t="s">
+        <v>117</v>
+      </c>
+      <c r="O29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20">
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" t="s">
+        <v>185</v>
+      </c>
+      <c r="L30" t="s">
+        <v>87</v>
+      </c>
+      <c r="M30" t="s">
+        <v>118</v>
+      </c>
+      <c r="N30" t="s">
+        <v>119</v>
+      </c>
+      <c r="O30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20">
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>185</v>
+      </c>
+      <c r="L31" t="s">
+        <v>87</v>
+      </c>
+      <c r="M31" t="s">
+        <v>120</v>
+      </c>
+      <c r="N31" t="s">
+        <v>121</v>
+      </c>
+      <c r="O31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20">
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" t="s">
+        <v>185</v>
+      </c>
+      <c r="L32" t="s">
+        <v>87</v>
+      </c>
+      <c r="M32" t="s">
+        <v>122</v>
+      </c>
+      <c r="N32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>185</v>
+      </c>
+      <c r="L33" t="s">
+        <v>87</v>
+      </c>
+      <c r="M33" t="s">
+        <v>124</v>
+      </c>
+      <c r="N33" t="s">
+        <v>125</v>
+      </c>
+      <c r="O33" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>185</v>
+      </c>
+      <c r="L34" t="s">
+        <v>87</v>
+      </c>
+      <c r="M34" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" t="s">
+        <v>127</v>
+      </c>
+      <c r="O34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>185</v>
+      </c>
+      <c r="L35" t="s">
+        <v>87</v>
+      </c>
+      <c r="M35" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" t="s">
+        <v>129</v>
+      </c>
+      <c r="O35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" t="s">
+        <v>185</v>
+      </c>
+      <c r="L36" t="s">
+        <v>87</v>
+      </c>
+      <c r="M36" t="s">
+        <v>130</v>
+      </c>
+      <c r="N36" t="s">
+        <v>131</v>
+      </c>
+      <c r="O36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="L37" t="s">
+        <v>87</v>
+      </c>
+      <c r="M37" t="s">
+        <v>132</v>
+      </c>
+      <c r="N37" t="s">
+        <v>133</v>
+      </c>
+      <c r="O37" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="L38" t="s">
+        <v>87</v>
+      </c>
+      <c r="M38" t="s">
+        <v>134</v>
+      </c>
+      <c r="N38" t="s">
+        <v>135</v>
+      </c>
+      <c r="O38" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="C39" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L39" t="s">
+        <v>87</v>
+      </c>
+      <c r="M39" t="s">
+        <v>136</v>
+      </c>
+      <c r="N39" t="s">
+        <v>137</v>
+      </c>
+      <c r="O39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="C40" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L40" t="s">
+        <v>87</v>
+      </c>
+      <c r="M40" t="s">
+        <v>138</v>
+      </c>
+      <c r="N40" t="s">
+        <v>139</v>
+      </c>
+      <c r="O40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="C41" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="L41" t="s">
+        <v>87</v>
+      </c>
+      <c r="M41" t="s">
+        <v>143</v>
+      </c>
+      <c r="N41" t="s">
         <v>144</v>
       </c>
-      <c r="I12" t="s">
+      <c r="O41" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="C42" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="L42" t="s">
+        <v>87</v>
+      </c>
+      <c r="M42" t="s">
+        <v>162</v>
+      </c>
+      <c r="N42" t="s">
+        <v>163</v>
+      </c>
+      <c r="O42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="C43" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="L43" t="s">
+        <v>87</v>
+      </c>
+      <c r="M43" t="s">
+        <v>164</v>
+      </c>
+      <c r="N43" t="s">
+        <v>165</v>
+      </c>
+      <c r="O43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="C44" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L44" t="s">
+        <v>87</v>
+      </c>
+      <c r="M44" t="s">
+        <v>166</v>
+      </c>
+      <c r="N44" t="s">
+        <v>167</v>
+      </c>
+      <c r="O44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="L45" t="s">
+        <v>87</v>
+      </c>
+      <c r="M45" t="s">
+        <v>140</v>
+      </c>
+      <c r="N45" t="s">
+        <v>141</v>
+      </c>
+      <c r="O45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="L46" t="s">
+        <v>87</v>
+      </c>
+      <c r="M46" t="s">
         <v>145</v>
       </c>
-      <c r="J12" t="s">
-        <v>143</v>
-      </c>
-      <c r="L12" t="s">
-        <v>87</v>
-      </c>
-      <c r="M12" t="s">
-        <v>155</v>
-      </c>
-      <c r="N12" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>87</v>
-      </c>
-      <c r="R12" t="s">
-        <v>155</v>
-      </c>
-      <c r="S12" t="s">
-        <v>156</v>
-      </c>
-      <c r="T12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="N46" t="s">
         <v>146</v>
       </c>
-      <c r="I13" t="s">
+      <c r="O46" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="L47" t="s">
+        <v>87</v>
+      </c>
+      <c r="M47" t="s">
         <v>147</v>
       </c>
-      <c r="J13" t="s">
-        <v>143</v>
-      </c>
-      <c r="L13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" t="s">
-        <v>157</v>
-      </c>
-      <c r="N13" t="s">
-        <v>158</v>
-      </c>
-      <c r="O13" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>87</v>
-      </c>
-      <c r="R13" t="s">
-        <v>91</v>
-      </c>
-      <c r="S13" t="s">
-        <v>92</v>
-      </c>
-      <c r="T13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="N47" t="s">
         <v>148</v>
       </c>
-      <c r="I14" t="s">
+      <c r="O47" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" t="s">
+        <v>87</v>
+      </c>
+      <c r="M48" t="s">
         <v>149</v>
       </c>
-      <c r="J14" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" t="s">
-        <v>92</v>
-      </c>
-      <c r="O14" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>87</v>
-      </c>
-      <c r="R14" t="s">
-        <v>93</v>
-      </c>
-      <c r="S14" t="s">
-        <v>94</v>
-      </c>
-      <c r="T14" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="N48" t="s">
         <v>150</v>
       </c>
-      <c r="I15" t="s">
+      <c r="O48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" t="str">
+        <f>LEFT(C40,18)</f>
+        <v>w169647963-400_ZAF</v>
+      </c>
+      <c r="D49" t="str">
+        <f>"at grid node - "&amp;C49</f>
+        <v>at grid node - w169647963-400_ZAF</v>
+      </c>
+      <c r="E49" t="s">
+        <v>186</v>
+      </c>
+      <c r="L49" t="s">
+        <v>87</v>
+      </c>
+      <c r="M49" t="s">
         <v>151</v>
       </c>
-      <c r="J15" t="s">
-        <v>143</v>
-      </c>
-      <c r="L15" t="s">
-        <v>87</v>
-      </c>
-      <c r="M15" t="s">
-        <v>93</v>
-      </c>
-      <c r="N15" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>87</v>
-      </c>
-      <c r="R15" t="s">
-        <v>172</v>
-      </c>
-      <c r="S15" t="s">
-        <v>173</v>
-      </c>
-      <c r="T15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="N49" t="s">
         <v>152</v>
       </c>
-      <c r="I16" t="s">
-        <v>153</v>
-      </c>
-      <c r="J16" t="s">
-        <v>143</v>
-      </c>
-      <c r="L16" t="s">
-        <v>87</v>
-      </c>
-      <c r="M16" t="s">
-        <v>159</v>
-      </c>
-      <c r="N16" t="s">
-        <v>160</v>
-      </c>
-      <c r="O16" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>87</v>
-      </c>
-      <c r="R16" t="s">
-        <v>174</v>
-      </c>
-      <c r="S16" t="s">
-        <v>175</v>
-      </c>
-      <c r="T16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" t="s">
-        <v>87</v>
-      </c>
-      <c r="M17" t="s">
-        <v>95</v>
-      </c>
-      <c r="N17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O17" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>87</v>
-      </c>
-      <c r="R17" t="s">
-        <v>176</v>
-      </c>
-      <c r="S17" t="s">
-        <v>177</v>
-      </c>
-      <c r="T17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="L18" t="s">
-        <v>87</v>
-      </c>
-      <c r="M18" t="s">
-        <v>97</v>
-      </c>
-      <c r="N18" t="s">
-        <v>98</v>
-      </c>
-      <c r="O18" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>87</v>
-      </c>
-      <c r="R18" t="s">
-        <v>178</v>
-      </c>
-      <c r="S18" t="s">
-        <v>179</v>
-      </c>
-      <c r="T18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>90</v>
-      </c>
-      <c r="L19" t="s">
-        <v>87</v>
-      </c>
-      <c r="M19" t="s">
-        <v>99</v>
-      </c>
-      <c r="N19" t="s">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>87</v>
-      </c>
-      <c r="R19" t="s">
-        <v>159</v>
-      </c>
-      <c r="S19" t="s">
-        <v>160</v>
-      </c>
-      <c r="T19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" t="s">
-        <v>87</v>
-      </c>
-      <c r="M20" t="s">
-        <v>101</v>
-      </c>
-      <c r="N20" t="s">
-        <v>102</v>
-      </c>
-      <c r="O20" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" t="s">
-        <v>87</v>
-      </c>
-      <c r="M21" t="s">
-        <v>161</v>
-      </c>
-      <c r="N21" t="s">
-        <v>162</v>
-      </c>
-      <c r="O21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" t="s">
-        <v>90</v>
-      </c>
-      <c r="L22" t="s">
-        <v>87</v>
-      </c>
-      <c r="M22" t="s">
-        <v>103</v>
-      </c>
-      <c r="N22" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L23" t="s">
-        <v>87</v>
-      </c>
-      <c r="M23" t="s">
-        <v>105</v>
-      </c>
-      <c r="N23" t="s">
-        <v>106</v>
-      </c>
-      <c r="O23" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24" t="s">
-        <v>90</v>
-      </c>
-      <c r="L24" t="s">
-        <v>87</v>
-      </c>
-      <c r="M24" t="s">
-        <v>107</v>
-      </c>
-      <c r="N24" t="s">
-        <v>108</v>
-      </c>
-      <c r="O24" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="L25" t="s">
-        <v>87</v>
-      </c>
-      <c r="M25" t="s">
-        <v>109</v>
-      </c>
-      <c r="N25" t="s">
-        <v>110</v>
-      </c>
-      <c r="O25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>90</v>
-      </c>
-      <c r="L26" t="s">
-        <v>87</v>
-      </c>
-      <c r="M26" t="s">
-        <v>111</v>
-      </c>
-      <c r="N26" t="s">
-        <v>112</v>
-      </c>
-      <c r="O26" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>90</v>
-      </c>
-      <c r="L27" t="s">
-        <v>87</v>
-      </c>
-      <c r="M27" t="s">
-        <v>113</v>
-      </c>
-      <c r="N27" t="s">
-        <v>114</v>
-      </c>
-      <c r="O27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" t="s">
-        <v>90</v>
-      </c>
-      <c r="L28" t="s">
-        <v>87</v>
-      </c>
-      <c r="M28" t="s">
-        <v>115</v>
-      </c>
-      <c r="N28" t="s">
-        <v>116</v>
-      </c>
-      <c r="O28" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" t="s">
-        <v>90</v>
-      </c>
-      <c r="L29" t="s">
-        <v>87</v>
-      </c>
-      <c r="M29" t="s">
-        <v>117</v>
-      </c>
-      <c r="N29" t="s">
-        <v>118</v>
-      </c>
-      <c r="O29" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" t="s">
-        <v>90</v>
-      </c>
-      <c r="L30" t="s">
-        <v>87</v>
-      </c>
-      <c r="M30" t="s">
-        <v>119</v>
-      </c>
-      <c r="N30" t="s">
-        <v>120</v>
-      </c>
-      <c r="O30" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" t="s">
-        <v>90</v>
-      </c>
-      <c r="L31" t="s">
-        <v>87</v>
-      </c>
-      <c r="M31" t="s">
-        <v>121</v>
-      </c>
-      <c r="N31" t="s">
-        <v>122</v>
-      </c>
-      <c r="O31" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" t="s">
-        <v>90</v>
-      </c>
-      <c r="L32" t="s">
-        <v>87</v>
-      </c>
-      <c r="M32" t="s">
-        <v>123</v>
-      </c>
-      <c r="N32" t="s">
-        <v>124</v>
-      </c>
-      <c r="O32" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" t="s">
-        <v>90</v>
-      </c>
-      <c r="L33" t="s">
-        <v>87</v>
-      </c>
-      <c r="M33" t="s">
-        <v>125</v>
-      </c>
-      <c r="N33" t="s">
-        <v>126</v>
-      </c>
-      <c r="O33" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" t="s">
-        <v>90</v>
-      </c>
-      <c r="L34" t="s">
-        <v>87</v>
-      </c>
-      <c r="M34" t="s">
-        <v>127</v>
-      </c>
-      <c r="N34" t="s">
-        <v>128</v>
-      </c>
-      <c r="O34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" t="s">
-        <v>90</v>
-      </c>
-      <c r="L35" t="s">
-        <v>87</v>
-      </c>
-      <c r="M35" t="s">
-        <v>129</v>
-      </c>
-      <c r="N35" t="s">
-        <v>130</v>
-      </c>
-      <c r="O35" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" t="s">
-        <v>90</v>
-      </c>
-      <c r="L36" t="s">
-        <v>87</v>
-      </c>
-      <c r="M36" t="s">
-        <v>131</v>
-      </c>
-      <c r="N36" t="s">
-        <v>132</v>
-      </c>
-      <c r="O36" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L37" t="s">
-        <v>87</v>
-      </c>
-      <c r="M37" t="s">
-        <v>133</v>
-      </c>
-      <c r="N37" t="s">
-        <v>134</v>
-      </c>
-      <c r="O37" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L38" t="s">
-        <v>87</v>
-      </c>
-      <c r="M38" t="s">
-        <v>135</v>
-      </c>
-      <c r="N38" t="s">
-        <v>136</v>
-      </c>
-      <c r="O38" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L39" t="s">
-        <v>87</v>
-      </c>
-      <c r="M39" t="s">
-        <v>137</v>
-      </c>
-      <c r="N39" t="s">
-        <v>138</v>
-      </c>
-      <c r="O39" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L40" t="s">
-        <v>87</v>
-      </c>
-      <c r="M40" t="s">
-        <v>139</v>
-      </c>
-      <c r="N40" t="s">
-        <v>140</v>
-      </c>
-      <c r="O40" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L41" t="s">
-        <v>87</v>
-      </c>
-      <c r="M41" t="s">
-        <v>144</v>
-      </c>
-      <c r="N41" t="s">
-        <v>145</v>
-      </c>
-      <c r="O41" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L42" t="s">
-        <v>87</v>
-      </c>
-      <c r="M42" t="s">
-        <v>163</v>
-      </c>
-      <c r="N42" t="s">
-        <v>164</v>
-      </c>
-      <c r="O42" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L43" t="s">
-        <v>87</v>
-      </c>
-      <c r="M43" t="s">
-        <v>165</v>
-      </c>
-      <c r="N43" t="s">
-        <v>166</v>
-      </c>
-      <c r="O43" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L44" t="s">
-        <v>87</v>
-      </c>
-      <c r="M44" t="s">
-        <v>167</v>
-      </c>
-      <c r="N44" t="s">
-        <v>168</v>
-      </c>
-      <c r="O44" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L45" t="s">
-        <v>87</v>
-      </c>
-      <c r="M45" t="s">
-        <v>141</v>
-      </c>
-      <c r="N45" t="s">
-        <v>142</v>
-      </c>
-      <c r="O45" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L46" t="s">
-        <v>87</v>
-      </c>
-      <c r="M46" t="s">
-        <v>146</v>
-      </c>
-      <c r="N46" t="s">
-        <v>147</v>
-      </c>
-      <c r="O46" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L47" t="s">
-        <v>87</v>
-      </c>
-      <c r="M47" t="s">
-        <v>148</v>
-      </c>
-      <c r="N47" t="s">
-        <v>149</v>
-      </c>
-      <c r="O47" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L48" t="s">
-        <v>87</v>
-      </c>
-      <c r="M48" t="s">
-        <v>150</v>
-      </c>
-      <c r="N48" t="s">
-        <v>151</v>
-      </c>
-      <c r="O48" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="49" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L49" t="s">
-        <v>87</v>
-      </c>
-      <c r="M49" t="s">
-        <v>152</v>
-      </c>
-      <c r="N49" t="s">
-        <v>153</v>
-      </c>
       <c r="O49" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
+      <c r="B50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" t="str">
+        <f>LEFT(C41,18)</f>
+        <v>w120941269-400_ZAF</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" ref="D50:D53" si="0">"at grid node - "&amp;C50</f>
+        <v>at grid node - w120941269-400_ZAF</v>
+      </c>
+      <c r="E50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15">
+      <c r="B51" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" t="str">
+        <f>LEFT(C42,18)</f>
+        <v>w107431792-400_ZAF</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="0"/>
+        <v>at grid node - w107431792-400_ZAF</v>
+      </c>
+      <c r="E51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15">
+      <c r="B52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" t="str">
+        <f>LEFT(C43,18)</f>
+        <v>w836844162-400_ZAF</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="0"/>
+        <v>at grid node - w836844162-400_ZAF</v>
+      </c>
+      <c r="E52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15">
+      <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" t="str">
+        <f>LEFT(C44,18)</f>
+        <v>w179140081-400_ZAF</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v>at grid node - w179140081-400_ZAF</v>
+      </c>
+      <c r="E53" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2050,7 +2258,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -2067,7 +2275,7 @@
     <col min="15" max="15" width="5.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -2114,7 +2322,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -2161,7 +2369,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -2208,7 +2416,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -2255,7 +2463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -2302,7 +2510,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2349,7 +2557,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -2396,7 +2604,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -2443,7 +2651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -2490,7 +2698,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2537,7 +2745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -2584,7 +2792,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -2631,7 +2839,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -2686,7 +2894,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X57"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -2700,7 +2908,7 @@
     <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:24">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -2714,7 +2922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:24">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:24">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -2760,7 +2968,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:24">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -2780,7 +2988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:24">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -2791,7 +2999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:24">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -2802,7 +3010,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:24">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -2813,7 +3021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:24">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -2827,7 +3035,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:24">
       <c r="P12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2844,7 +3052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:24">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -2871,7 +3079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:24">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -2910,7 +3118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:24">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -2949,7 +3157,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:24">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -2982,7 +3190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:24">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -3017,7 +3225,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:24">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -3052,7 +3260,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:24">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -3087,7 +3295,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:24">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3330,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:24">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -3157,7 +3365,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:24">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -3192,7 +3400,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:24">
       <c r="P23" s="2" t="s">
         <v>31</v>
       </c>
@@ -3218,7 +3426,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:24">
       <c r="P24" s="2" t="s">
         <v>31</v>
       </c>
@@ -3244,12 +3452,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:24">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:24">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -3266,7 +3474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:24">
       <c r="C29" t="s">
         <v>17</v>
       </c>
@@ -3277,7 +3485,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:24">
       <c r="C30" t="s">
         <v>53</v>
       </c>
@@ -3288,7 +3496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:24">
       <c r="C31" t="s">
         <v>17</v>
       </c>
@@ -3299,7 +3507,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:24">
       <c r="D32" t="s">
         <v>7</v>
       </c>
@@ -3310,7 +3518,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:7">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -3321,7 +3529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:7">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -3332,7 +3540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:7">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -3346,12 +3554,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:7">
       <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:7">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -3362,7 +3570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:7">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -3373,7 +3581,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:7">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -3384,7 +3592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:7">
       <c r="C42" t="s">
         <v>57</v>
       </c>
@@ -3395,7 +3603,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:7">
       <c r="C43" t="s">
         <v>55</v>
       </c>
@@ -3406,7 +3614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:7">
       <c r="C44" t="s">
         <v>56</v>
       </c>
@@ -3417,12 +3625,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:7">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:7">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -3436,7 +3644,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:13">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -3450,7 +3658,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -3464,12 +3672,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:13">
       <c r="C54" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:13">
       <c r="C55" t="s">
         <v>25</v>
       </c>
@@ -3504,7 +3712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:13">
       <c r="C56" t="s">
         <v>78</v>
       </c>
@@ -3524,7 +3732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:13">
       <c r="C57" t="s">
         <v>78</v>
       </c>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359BF10A-74FD-4CC7-A95C-64D4AA39AD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3381081F-F5C1-4909-865B-59A9812ECAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="191">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -655,13 +655,22 @@
     </r>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
     <t>CCGT,CCGT + CCS</t>
   </si>
   <si>
     <t>gas offered only on coastal buses</t>
+  </si>
+  <si>
+    <t>w219384657-765_ZAF</t>
+  </si>
+  <si>
+    <t>w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+  </si>
+  <si>
+    <t>Nuclear large</t>
   </si>
 </sst>
 </file>
@@ -740,6 +749,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>557212</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>2659</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>515646</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B635E193-7FA8-FC82-EA0C-12935B3B55FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4443412" y="9956284"/>
+          <a:ext cx="5787734" cy="3116778"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1005,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T53"/>
+  <dimension ref="B3:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:20">
@@ -1112,7 +1170,7 @@
         <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G11" t="s">
         <v>87</v>
@@ -1162,7 +1220,7 @@
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G12" t="s">
         <v>87</v>
@@ -1212,7 +1270,7 @@
         <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G13" t="s">
         <v>87</v>
@@ -1262,7 +1320,7 @@
         <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G14" t="s">
         <v>87</v>
@@ -1312,7 +1370,7 @@
         <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G15" t="s">
         <v>87</v>
@@ -1362,7 +1420,7 @@
         <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G16" t="s">
         <v>87</v>
@@ -1412,7 +1470,7 @@
         <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s">
         <v>87</v>
@@ -1450,7 +1508,7 @@
         <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s">
         <v>87</v>
@@ -1488,7 +1546,7 @@
         <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L19" t="s">
         <v>87</v>
@@ -1526,7 +1584,7 @@
         <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L20" t="s">
         <v>87</v>
@@ -1552,7 +1610,7 @@
         <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s">
         <v>87</v>
@@ -1578,7 +1636,7 @@
         <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s">
         <v>87</v>
@@ -1604,7 +1662,7 @@
         <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s">
         <v>87</v>
@@ -1630,7 +1688,7 @@
         <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s">
         <v>87</v>
@@ -1656,7 +1714,7 @@
         <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s">
         <v>87</v>
@@ -1682,7 +1740,7 @@
         <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s">
         <v>87</v>
@@ -1708,7 +1766,7 @@
         <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L27" t="s">
         <v>87</v>
@@ -1734,7 +1792,7 @@
         <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s">
         <v>87</v>
@@ -1760,7 +1818,7 @@
         <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s">
         <v>87</v>
@@ -1786,7 +1844,7 @@
         <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s">
         <v>87</v>
@@ -1812,7 +1870,7 @@
         <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s">
         <v>87</v>
@@ -1838,7 +1896,7 @@
         <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s">
         <v>87</v>
@@ -1864,7 +1922,7 @@
         <v>133</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s">
         <v>87</v>
@@ -1890,7 +1948,7 @@
         <v>135</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s">
         <v>87</v>
@@ -1916,7 +1974,7 @@
         <v>137</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s">
         <v>87</v>
@@ -1942,7 +2000,7 @@
         <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s">
         <v>87</v>
@@ -1987,7 +2045,7 @@
     </row>
     <row r="39" spans="2:15">
       <c r="C39" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L39" t="s">
         <v>87</v>
@@ -2171,7 +2229,7 @@
         <v>at grid node - w169647963-400_ZAF</v>
       </c>
       <c r="E49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L49" t="s">
         <v>87</v>
@@ -2199,7 +2257,7 @@
         <v>at grid node - w120941269-400_ZAF</v>
       </c>
       <c r="E50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="2:15">
@@ -2215,7 +2273,7 @@
         <v>at grid node - w107431792-400_ZAF</v>
       </c>
       <c r="E51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="2:15">
@@ -2231,7 +2289,7 @@
         <v>at grid node - w836844162-400_ZAF</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="2:15">
@@ -2247,11 +2305,91 @@
         <v>at grid node - w179140081-400_ZAF</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15">
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15">
+      <c r="B56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15">
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" ref="D57:D60" si="1">"at grid node - "&amp;C57</f>
+        <v>at grid node - w836844162-400_ZAF</v>
+      </c>
+      <c r="E57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15">
+      <c r="B58" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="1"/>
+        <v>at grid node - w219384657-765_ZAF</v>
+      </c>
+      <c r="E58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15">
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="1"/>
+        <v>at grid node - w102682082-400_ZAF</v>
+      </c>
+      <c r="E59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15">
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="1"/>
+        <v>at grid node - w90454383-400_ZAF</v>
+      </c>
+      <c r="E60" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3381081F-F5C1-4909-865B-59A9812ECAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B85DCB-0013-4A33-B3FC-64440F3A8634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="192">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>Nuclear large</t>
+  </si>
+  <si>
+    <t>AF</t>
   </si>
 </sst>
 </file>
@@ -3692,6 +3695,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="36" spans="3:7">
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>191</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
     <row r="38" spans="3:7">
       <c r="C38" t="s">
         <v>20</v>
